--- a/task151/golden/pa_bonus_accrual_2027.xlsx
+++ b/task151/golden/pa_bonus_accrual_2027.xlsx
@@ -8,9 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accrual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IL stints since 2024" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PA bonuses paid 2024-2026" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Look-back (FIN-14 4.4)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IL stints since 2024" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PA bonuses paid 2024-2026" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Accrual'!$5:$5</definedName>
@@ -21,13 +22,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="166" formatCode="$#,##0"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,6 +47,7 @@
     <font>
       <i val="1"/>
     </font>
+    <font/>
   </fonts>
   <fills count="3">
     <fill>
@@ -76,7 +79,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -92,6 +95,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -478,7 +483,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Plate-appearance bonuses, 2027 free-agent hitters: accrual at signing $3,500,000</t>
+          <t>Plate-appearance bonuses, 2027 free-agent hitters: accrual at signing $4,250,000</t>
         </is>
       </c>
     </row>
@@ -541,271 +546,271 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Jairo Calderón</t>
+          <t>Sawyer Lusk</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
         <v>46350</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>350000</v>
+        <v>320000</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.7826</v>
+        <v>0.7438</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>273923.61</v>
+        <v>238000</v>
       </c>
     </row>
     <row r="7">
       <c r="D7" t="n">
-        <v>525</v>
+        <v>575</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>350000</v>
+        <v>320000</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.7056</v>
+        <v>0.5681</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>246944.44</v>
+        <v>181777.78</v>
       </c>
     </row>
     <row r="8">
       <c r="D8" t="n">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>350000</v>
+        <v>320000</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.5083</v>
+        <v>0.2938</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>177916.67</v>
+        <v>94000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Jairo Calderón, accrual</t>
+          <t>Sawyer Lusk, accrual</t>
         </is>
       </c>
       <c r="G9" s="5" t="n">
-        <v>698784.72</v>
+        <v>513777.78</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>700000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Kevin Weeks</t>
+          <t>Andres Rivas</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
         <v>46356</v>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>475</v>
+        <v>525</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>450000</v>
+        <v>750000</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.7632</v>
+        <v>0.6667</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>343437.5</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="11">
       <c r="D11" t="n">
-        <v>550</v>
+        <v>575</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>450000</v>
+        <v>750000</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>0.6104000000000001</v>
+        <v>0.5319</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>274687.5</v>
+        <v>398958.33</v>
       </c>
     </row>
     <row r="12">
       <c r="D12" t="n">
-        <v>625</v>
+        <v>650</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>450000</v>
+        <v>750000</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.3792</v>
+        <v>0.1493</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>170625</v>
+        <v>111979.17</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Kevin Weeks, accrual</t>
+          <t>Andres Rivas, accrual</t>
         </is>
       </c>
       <c r="G13" s="5" t="n">
-        <v>788750</v>
+        <v>1010937.5</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>800000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ramon Figueroa</t>
+          <t>Drew Brock</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
         <v>46359</v>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>500000</v>
+        <v>330000</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.6986</v>
+        <v>0.791</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>349305.56</v>
+        <v>261020.83</v>
       </c>
     </row>
     <row r="15">
       <c r="D15" t="n">
-        <v>550</v>
+        <v>525</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>500000</v>
+        <v>330000</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0.5757</v>
+        <v>0.6306</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>287847.22</v>
+        <v>208083.33</v>
       </c>
     </row>
     <row r="16">
       <c r="D16" t="n">
-        <v>625</v>
+        <v>600</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>500000</v>
+        <v>330000</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.3389</v>
+        <v>0.359</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>169444.44</v>
+        <v>118479.17</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Ramon Figueroa, accrual</t>
+          <t>Drew Brock, accrual</t>
         </is>
       </c>
       <c r="G17" s="5" t="n">
-        <v>806597.22</v>
+        <v>587583.33</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>800000</v>
+        <v>600000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Eric Dobbs</t>
+          <t>Ángel Medina</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
         <v>46364</v>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>525</v>
+        <v>500</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>560000</v>
+        <v>730000</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>0.6104000000000001</v>
+        <v>0.6597</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>341833.33</v>
+        <v>481597.22</v>
       </c>
     </row>
     <row r="19">
       <c r="D19" t="n">
-        <v>575</v>
+        <v>525</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>560000</v>
+        <v>730000</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>0.4549</v>
+        <v>0.5951</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>254722.22</v>
+        <v>434451.39</v>
       </c>
     </row>
     <row r="20">
       <c r="D20" t="n">
-        <v>650</v>
+        <v>575</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>560000</v>
+        <v>730000</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>0.0125</v>
+        <v>0.3868</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>7000</v>
+        <v>282368.06</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>Eric Dobbs, accrual</t>
+          <t>Ángel Medina, accrual</t>
         </is>
       </c>
       <c r="G21" s="5" t="n">
-        <v>603555.5600000001</v>
+        <v>1198416.67</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>600000</v>
+        <v>1200000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Dylan Harlow</t>
+          <t>Mike Meeks</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
@@ -815,57 +820,57 @@
         <v>9</v>
       </c>
       <c r="D22" t="n">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>360000</v>
+        <v>720000</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>0.7181</v>
+        <v>0.6306</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>258500</v>
+        <v>454000</v>
       </c>
     </row>
     <row r="23">
       <c r="D23" t="n">
-        <v>500</v>
+        <v>550</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>360000</v>
+        <v>720000</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>0.5965</v>
+        <v>0.4437</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>214750</v>
+        <v>319500</v>
       </c>
     </row>
     <row r="24">
       <c r="D24" t="n">
-        <v>575</v>
+        <v>600</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>360000</v>
+        <v>720000</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>0.3472</v>
+        <v>0.191</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>125000</v>
+        <v>137500</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>Dylan Harlow, accrual</t>
+          <t>Mike Meeks, accrual</t>
         </is>
       </c>
       <c r="G25" s="5" t="n">
-        <v>598250</v>
+        <v>911000</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>600000</v>
+        <v>900000</v>
       </c>
     </row>
     <row r="26">
@@ -875,10 +880,10 @@
         </is>
       </c>
       <c r="G26" s="5" t="n">
-        <v>3495937.5</v>
+        <v>4221715.28</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>3500000</v>
+        <v>4250000</v>
       </c>
     </row>
     <row r="28">
@@ -947,31 +952,31 @@
         </is>
       </c>
       <c r="B30" s="10" t="n">
-        <v>4.727</v>
+        <v>4.716</v>
       </c>
       <c r="C30" s="10" t="n">
-        <v>4.611</v>
+        <v>4.596</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>4.489</v>
+        <v>4.481</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>4.378</v>
+        <v>4.366</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>4.258</v>
+        <v>4.247</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>4.152</v>
+        <v>4.139</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>4.049</v>
+        <v>4.038</v>
       </c>
       <c r="I30" s="10" t="n">
-        <v>3.944</v>
+        <v>3.936</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>3.838</v>
+        <v>3.828</v>
       </c>
     </row>
   </sheetData>
@@ -981,6 +986,298 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="66" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>FIN-14 4.4 look-back: 748 hitter-seasons, 2023 to 2026; the basis with the lowest score is used</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Each basis applied to each season with what was published before it began, to every hitter in a starting lineup of that season's January 31 depth charts with 100 plate appearances in each of the two seasons before; score: the average squared difference between the probability of 450, 500, 550, 600 and 650 plate appearances and the outcome (1 reached, 0 not).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Above the basis used</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2027 accrual on this basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Non-catcher regulars' seasons of starts at the player's 2027 slot (used)</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="n">
+        <v>0.173</v>
+      </c>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="5" t="n">
+        <v>4250000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>The same, the last three seasons only</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n">
+        <v>0.173</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>4250000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>The same, each season's plate appearances rescaled to the slot</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="n">
+        <v>0.1732</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>4250000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Vendor's projection with a normal band from its misses</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="n">
+        <v>0.2254</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>6250000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Vendor's projection plus each of its past misses</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="n">
+        <v>0.2206</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>0.2748</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>7250000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>The player's own last three seasons</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="n">
+        <v>0.2698</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>0.5595</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>7750000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Every lineup regular's plate appearances, catchers in, any slot</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="n">
+        <v>0.2182</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>0.2609</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>4500000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>Non-catcher regulars' plate appearances, any slot</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="n">
+        <v>0.1845</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>0.0665</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>5250000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Every lineup regular's starts at the player's slot, catchers in</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>0.1211</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>3750000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>Opening-day starters' seasons at the player's slot</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="n">
+        <v>0.1766</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>0.0207</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>4000000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Regulars who started their club's first game, at the slot</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="n">
+        <v>0.1751</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>4750000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>Hitters with 400 or more plate appearances, at the slot</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n">
+        <v>0.1792</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>4500000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>The regulars' seasons moved 10 per cent toward the player's record</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="n">
+        <v>0.1758</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>0.0161</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>4750000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>Regression on the vendor's projection, slot and catching</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="n">
+        <v>0.1749</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>0.0107</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>4250000</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>The bases that tie the one used (the last three seasons; plate appearances rescaled) give the same accrual. Accruals to the nearest $250,000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Sources: hvbd_winter_depth_charts_2021_2026.xlsx; hvbd_hitter_projections_2022_2027.csv; the batting lines 2021 to 2026.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1002,7 +1299,7 @@
     <row r="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>Injured-list stints of the five since Opening Day 2024: nine stints, 235 regular-season days</t>
+          <t>Injured-list stints of the five since Opening Day 2024: nine stints, 233 regular-season days</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1348,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jairo Calderón</t>
+          <t>Sawyer Lusk</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1076,16 +1373,16 @@
         </is>
       </c>
       <c r="G4" s="4" t="n">
-        <v>45482</v>
+        <v>45484</v>
       </c>
       <c r="H4" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Eric Dobbs</t>
+          <t>Ángel Medina</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1099,10 +1396,10 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
+        <v>45432</v>
+      </c>
+      <c r="E5" s="4" t="n">
         <v>45431</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>45430</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1113,13 +1410,13 @@
         <v>45441</v>
       </c>
       <c r="H5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Eric Dobbs</t>
+          <t>Ángel Medina</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1153,7 +1450,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dylan Harlow</t>
+          <t>Mike Meeks</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1178,16 +1475,16 @@
         </is>
       </c>
       <c r="G7" s="4" t="n">
-        <v>45522</v>
+        <v>45521</v>
       </c>
       <c r="H7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ramon Figueroa</t>
+          <t>Drew Brock</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1201,10 +1498,10 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>45521</v>
+        <v>45520</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>45519</v>
+        <v>45518</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1212,7 +1509,7 @@
         </is>
       </c>
       <c r="G8" s="4" t="n">
-        <v>45532</v>
+        <v>45531</v>
       </c>
       <c r="H8" t="n">
         <v>13</v>
@@ -1221,7 +1518,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Dylan Harlow</t>
+          <t>Mike Meeks</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1246,16 +1543,16 @@
         </is>
       </c>
       <c r="G9" s="4" t="n">
-        <v>45758</v>
+        <v>45756</v>
       </c>
       <c r="H9" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ramon Figueroa</t>
+          <t>Drew Brock</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1289,7 +1586,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kevin Weeks</t>
+          <t>Andres Rivas</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1323,7 +1620,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Jairo Calderón</t>
+          <t>Sawyer Lusk</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1373,7 +1670,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1417,11 +1714,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Carson Bickford</t>
+          <t>Edwin Cedeno</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>420000</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="5">
@@ -1430,11 +1727,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Andrés Acevedo</t>
+          <t>Jonathan Vasquez</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>300000</v>
+        <v>125000</v>
       </c>
     </row>
     <row r="6">
@@ -1447,7 +1744,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>720000</v>
+        <v>325000</v>
       </c>
     </row>
     <row r="8">
@@ -1456,11 +1753,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Zach Strickland</t>
+          <t>Jonathan Vasquez</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>225000</v>
+        <v>375000</v>
       </c>
     </row>
     <row r="9">
@@ -1469,37 +1766,37 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Shota Nakagawa</t>
+          <t>Gregorio Candelario</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>100000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>2025</v>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Juan Nunez</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>225000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Total 2025</t>
         </is>
       </c>
-      <c r="C10" s="9" t="n">
-        <v>325000</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Elijah Mosley</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>187500</v>
+      <c r="C11" s="9" t="n">
+        <v>900000</v>
       </c>
     </row>
     <row r="13">
@@ -1508,11 +1805,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Shota Nakagawa</t>
+          <t>Jacob Briggs</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>150000</v>
+        <v>262500</v>
       </c>
     </row>
     <row r="14">
@@ -1521,11 +1818,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kody Bagwell</t>
+          <t>Gregorio Candelario</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>87500</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="15">
@@ -1538,7 +1835,7 @@
         </is>
       </c>
       <c r="C15" s="9" t="n">
-        <v>425000</v>
+        <v>412500</v>
       </c>
     </row>
     <row r="17">
@@ -1574,7 +1871,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1587,37 +1884,37 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>As of December 11, 2026 (files pulled that afternoon). Prepared by Harry Barnes, Controller.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
-        <is>
-          <t>Accrual under FIN-14 4.2 to 4.4: each plate-appearance bonus at its amount times the probability that the player reaches its threshold in the 2027 championship season, assessed at signing, the player taken as staying with the Club in his planned role (lineup slot in ral_depth_chart_2027.xlsx).</t>
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>Accrual under FIN-14 4.2 and 4.3: each plate-appearance bonus at its amount times the probability that the player reaches its threshold in the 2027 championship season, assessed at signing, the contract taken as standing all season with the player in his planned role (lineup slot in ral_depth_chart_2027.xlsx) and his health and playing time left in the probability. Basis chosen by the FIN-14 4.4 look-back (sheet Look-back).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Plate appearances as the term sheets define them: championship season, for the Club; postseason and rehabilitation-assignment plate appearances excluded.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Comparison seasons: the non-catchers in the lineups of hvbd_winter_depth_charts_2021_2026.xlsx, 1,440 seasons; starts counted for every club the player started for that season, from lsf_batting_2021_2024.txt (through lsf_player_id_crosswalk.csv) and lsf_batting_2025_2026.csv.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>Rounding: each player's accrual to the nearest $100,000 and the total to the nearest $250,000, both from the unrounded line amounts.</t>
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Rounding (FIN-14 6): each player's accrual to the nearest $100,000 and the total to the nearest $250,000, both from the unrounded line amounts; the rounded player figures add to $4,200,000.</t>
         </is>
       </c>
     </row>

--- a/task151/golden/pa_bonus_accrual_2027.xlsx
+++ b/task151/golden/pa_bonus_accrual_2027.xlsx
@@ -1003,7 +1003,7 @@
     <row r="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>FIN-14 4.4 look-back: 748 hitter-seasons, 2023 to 2026; the basis with the lowest score is used</t>
+          <t>FIN-14 4.4 look-back (working paper CF-14.4): 748 hitter-seasons, 2023 to 2026; the basis with the lowest score is used</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1261,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>The bases that tie the one used (the last three seasons; plate appearances rescaled) give the same accrual. Accruals to the nearest $250,000.</t>
+          <t>The basis used prices each tested hitter from the seasons of his own group: a catcher from the catcher regulars' seasons, every other hitter from the non-catcher regulars'. The bases that tie it (the last three seasons; plate appearances rescaled) give the same accrual. Accruals to the nearest $250,000.</t>
         </is>
       </c>
     </row>

--- a/task151/golden/pa_bonus_accrual_2027.xlsx
+++ b/task151/golden/pa_bonus_accrual_2027.xlsx
@@ -9,12 +9,12 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accrual" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Look-back (FIN-14 4.4)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IL stints since 2024" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PA bonuses paid 2024-2026" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Other PT bonuses 2023-2025" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Accrual'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Other PT bonuses 2023-2025'!$3:$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -22,12 +22,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="166" formatCode="$#,##0"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
     <numFmt numFmtId="168" formatCode="0.0000"/>
+    <numFmt numFmtId="169" formatCode="$#,##0;($#,##0)"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -62,7 +63,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -75,11 +76,16 @@
         <color rgb="00999999"/>
       </bottom>
     </border>
+    <border>
+      <top style="thin">
+        <color rgb="00999999"/>
+      </top>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -97,6 +103,8 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1281,597 +1289,612 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>Injured-list stints of the five since Opening Day 2024: nine stints, 233 regular-season days</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+          <t>Other playing-time bonuses paid: $580,000 for 2023, $1,080,000 for 2024, $1,230,000 for 2025 (payroll register through December 11, 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>Season</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>Player</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Club</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Contract terms (each season)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Placed (transaction)</t>
+          <t>Season-end payment</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Took effect</t>
+          <t>January payment</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Ended</t>
+          <t>Award in season-end line</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Date ended</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Regular-season days</t>
+          <t>Paid for the season</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Sawyer Lusk</t>
-        </is>
+      <c r="A4" t="n">
+        <v>2023</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Omaha Cattlemen</t>
+          <t>Yordy Benítez</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>10-day to 60-day</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>45418</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>45416</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Activated</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>45484</v>
-      </c>
-      <c r="H4" t="n">
-        <v>68</v>
+          <t>Innings pitched: $55,000 each for 140 and 160</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>55000</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>55000</v>
+      </c>
+      <c r="F4" s="13" t="n"/>
+      <c r="G4" s="5" t="n">
+        <v>110000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Ángel Medina</t>
-        </is>
+      <c r="A5" t="n">
+        <v>2023</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Memphis Riverboats</t>
+          <t>Julio Casilla</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>10-day</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>45432</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>45431</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Activated</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>45441</v>
-      </c>
-      <c r="H5" t="n">
-        <v>10</v>
+          <t>Relief appearances: $30,000 each for 40, 50 and 60</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F5" s="13" t="n"/>
+      <c r="G5" s="5" t="n">
+        <v>60000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Ángel Medina</t>
-        </is>
+      <c r="A6" t="n">
+        <v>2023</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Memphis Riverboats</t>
+          <t>Carlos Lara</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>10-day</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>45446</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>45445</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Activated</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>45459</v>
-      </c>
-      <c r="H6" t="n">
-        <v>14</v>
+          <t>Innings pitched: $70,000 each for 150, 170 and 190</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>70000</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>70000</v>
+      </c>
+      <c r="F6" s="13" t="n"/>
+      <c r="G6" s="5" t="n">
+        <v>140000</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Mike Meeks</t>
-        </is>
+      <c r="A7" t="n">
+        <v>2023</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Las Vegas Silverados</t>
+          <t>Santiago Ruiz</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>7-day</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>45514</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>45513</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Activated</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>45521</v>
-      </c>
-      <c r="H7" t="n">
-        <v>8</v>
+          <t>Days on the Active List: $75,000 each for 120 and 150; relief appearances: $75,000 each for 45 and 55</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>125000</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>75000</v>
+      </c>
+      <c r="F7" s="13" t="n">
+        <v>-50000</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>150000</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Drew Brock</t>
-        </is>
+      <c r="A8" t="n">
+        <v>2023</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Buffalo Millers</t>
+          <t>Max White</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>10-day</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>45520</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>45518</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Activated</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>45531</v>
-      </c>
-      <c r="H8" t="n">
-        <v>13</v>
+          <t>Innings pitched: $60,000 each for 160 and 180; games started: $60,000 each for 28 and 32</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>60000</v>
+      </c>
+      <c r="F8" s="13" t="n"/>
+      <c r="G8" s="5" t="n">
+        <v>120000</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Mike Meeks</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Las Vegas Silverados</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>10-day</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>45744</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>45741</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Activated</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>45756</v>
-      </c>
-      <c r="H9" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Drew Brock</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Buffalo Millers / Oklahoma City Drovers</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>10-day to 60-day</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>46188</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>46186</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Activated</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>46262</v>
-      </c>
-      <c r="H10" t="n">
-        <v>76</v>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Total 2023</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>340000</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>290000</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>-50000</v>
+      </c>
+      <c r="G9" s="14" t="n">
+        <v>580000</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Andres Rivas</t>
-        </is>
+      <c r="A11" t="n">
+        <v>2024</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sacramento Prospectors</t>
+          <t>Carlos Lara</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>10-day</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>46213</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>46211</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Activated</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>46225</v>
-      </c>
-      <c r="H11" t="n">
-        <v>14</v>
+          <t>Innings pitched: $100,000 each for 150, 165 and 180; games started: $50,000 each for 25 and 30</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>150000</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>150000</v>
+      </c>
+      <c r="F11" s="13" t="n"/>
+      <c r="G11" s="5" t="n">
+        <v>300000</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Sawyer Lusk</t>
-        </is>
+      <c r="A12" t="n">
+        <v>2024</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Omaha Cattlemen</t>
+          <t>Joe Livingston</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>10-day</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>46278</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>46276</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Reinstated</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>46329</v>
-      </c>
-      <c r="H12" t="n">
-        <v>17</v>
+          <t>Relief appearances: $50,000 each for 50, 60 and 70</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>90000</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>-40000</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Tyler Reed</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Innings pitched: $85,000 each for 150 and 175; games started: $85,000 each for 28 and 32</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>85000</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>85000</v>
+      </c>
+      <c r="F13" s="13" t="n"/>
+      <c r="G13" s="5" t="n">
+        <v>170000</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Took effect: the report's first date of reinstatement less the list's minimum period (League Rules 22.2). Days counted from the later of that date and Opening Day through the day before reinstatement, or the last scheduled day (22.7).</t>
-        </is>
+      <c r="A14" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Sam Robertson</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Relief appearances: $45,000 each for 50 and 60</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>45000</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>45000</v>
+      </c>
+      <c r="F14" s="13" t="n"/>
+      <c r="G14" s="5" t="n">
+        <v>90000</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Sources: lsf_transactions_2024_2026.json; league_office_il_report_2024_2026.csv; league_calendar_2021_2027.csv.</t>
+      <c r="A15" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Santiago Ruiz</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Days on the Active List: $75,000 each for 120 and 150; relief appearances: $75,000 each for 45 and 55</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>150000</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>150000</v>
+      </c>
+      <c r="F15" s="13" t="n"/>
+      <c r="G15" s="5" t="n">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Max White</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Innings pitched: $60,000 each for 160 and 180; games started: $60,000 each for 28 and 32</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>60000</v>
+      </c>
+      <c r="F16" s="13" t="n"/>
+      <c r="G16" s="5" t="n">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Total 2024</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>580000</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>540000</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>-40000</v>
+      </c>
+      <c r="G17" s="14" t="n">
+        <v>1080000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Johnny Blair</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Games started: $70,000 each for 28 and 32</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>70000</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>70000</v>
+      </c>
+      <c r="F19" s="13" t="n"/>
+      <c r="G19" s="5" t="n">
+        <v>140000</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Carlos Lara</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Innings pitched: $100,000 each for 150, 165 and 180; games started: $50,000 each for 25 and 30</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>100000</v>
+      </c>
+      <c r="F20" s="13" t="n"/>
+      <c r="G20" s="5" t="n">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Joe Livingston</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Relief appearances: $50,000 each for 50, 60 and 70</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F21" s="13" t="n"/>
+      <c r="G21" s="5" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Gilmar Pietersz</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Relief appearances: $60,000 each for 55 and 65</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>110000</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>60000</v>
+      </c>
+      <c r="F22" s="13" t="n">
+        <v>-50000</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Tyler Reed</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Innings pitched: $85,000 each for 150 and 175; games started: $85,000 each for 28 and 32</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>170000</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>170000</v>
+      </c>
+      <c r="F23" s="13" t="n"/>
+      <c r="G23" s="5" t="n">
+        <v>340000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Sam Robertson</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Relief appearances: $45,000 each for 50 and 60</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>45000</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>45000</v>
+      </c>
+      <c r="F24" s="13" t="n"/>
+      <c r="G24" s="5" t="n">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Max White</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Innings pitched: $60,000 each for 160 and 180; games started: $60,000 each for 28 and 32</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>120000</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>120000</v>
+      </c>
+      <c r="F25" s="13" t="n"/>
+      <c r="G25" s="5" t="n">
+        <v>240000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Total 2025</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="n">
+        <v>665000</v>
+      </c>
+      <c r="E26" s="14" t="n">
+        <v>615000</v>
+      </c>
+      <c r="F26" s="14" t="n">
+        <v>-50000</v>
+      </c>
+      <c r="G26" s="14" t="n">
+        <v>1230000</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>The pitchers' bonuses are paid half in the season-end run (October 15) and half on the following January 15. Before the January 2026 HRIS cutover the legacy payroll put the season-end halves on E45 OTHER BONUS and the January halves on E40 PERF BONUS; from January 2026 both are BPA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>An All-Star bonus paid in the same legacy season-end line is taken out (Ruiz 2023, Livingston 2024, Pietersz 2025). White's Cy Young bonus (November 15, 2024) is an award, not playing time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Legacy number 01661 was reissued: Yordy Benítez's lines to January 2024, Gilmar Pietersz's from 2025; legacy lines are taken by the name on the line. The October 2025 void and reissue to Reed counts once.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Sources: ral_payroll_player_earnings_2023_2026.csv; ral_hris_legacy_employee_map.csv; ral_player_contract_register_2023_2026.xlsx.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>Plate-appearance bonuses paid by the Club, by the season they were earned (payroll register through December 11, 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Season</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Player</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Edwin Cedeno</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n">
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Jonathan Vasquez</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>125000</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Total 2024</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="n">
-        <v>325000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Jonathan Vasquez</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>375000</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Gregorio Candelario</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Juan Nunez</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>225000</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Total 2025</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="n">
-        <v>900000</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Jacob Briggs</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>262500</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Gregorio Candelario</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="n">
-        <v>150000</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>Total 2026</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="n">
-        <v>412500</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026: the second halves are payable on January 15, 2027.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Each playing-time payment carries a season's plate-appearance and games-started bonuses together; the plate-appearance part is half the plate-appearance lines the player reached for the Club, for each payment made.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2024 first halves are inside the legacy PERF BONUS lines of October 15, 2024, which carry every performance bonus paid that day. Pitchers' games and innings bonuses on the playing-time code are excluded.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Sources: ral_payroll_player_earnings_2023_2026.csv; ral_player_contract_register_2024_2026.xlsx; the batting lines for plate appearances by club.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1884,35 +1907,35 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>As of December 11, 2026 (files pulled that afternoon). Prepared by Harry Barnes, Controller.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>Accrual under FIN-14 4.2 and 4.3: each plate-appearance bonus at its amount times the probability that the player reaches its threshold in the 2027 championship season, assessed at signing, the contract taken as standing all season with the player in his planned role (lineup slot in ral_depth_chart_2027.xlsx) and his health and playing time left in the probability. Basis chosen by the FIN-14 4.4 look-back (sheet Look-back).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>Plate appearances as the term sheets define them: championship season, for the Club; postseason and rehabilitation-assignment plate appearances excluded.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Comparison seasons: the non-catchers in the lineups of hvbd_winter_depth_charts_2021_2026.xlsx, 1,440 seasons; starts counted for every club the player started for that season, from lsf_batting_2021_2024.txt (through lsf_player_id_crosswalk.csv) and lsf_batting_2025_2026.csv.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Rounding (FIN-14 6): each player's accrual to the nearest $100,000 and the total to the nearest $250,000, both from the unrounded line amounts; the rounded player figures add to $4,200,000.</t>
         </is>

--- a/task151/golden/pa_bonus_accrual_2027.xlsx
+++ b/task151/golden/pa_bonus_accrual_2027.xlsx
@@ -1291,7 +1291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1301,12 +1301,13 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>Other playing-time bonuses paid: $580,000 for 2023, $1,080,000 for 2024, $1,230,000 for 2025 (payroll register through December 11, 2026)</t>
+          <t>Other playing-time bonuses paid: $525,000 for 2023, $1,005,000 for 2024, $1,085,000 for 2025 (payroll register through December 11, 2026)</t>
         </is>
       </c>
     </row>
@@ -1342,6 +1343,11 @@
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Deferred salary in season-end line</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Paid for the season</t>
         </is>
@@ -1362,14 +1368,15 @@
         </is>
       </c>
       <c r="D4" s="5" t="n">
+        <v>310000</v>
+      </c>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="13" t="n"/>
+      <c r="G4" s="13" t="n">
+        <v>-255000</v>
+      </c>
+      <c r="H4" s="5" t="n">
         <v>55000</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>55000</v>
-      </c>
-      <c r="F4" s="13" t="n"/>
-      <c r="G4" s="5" t="n">
-        <v>110000</v>
       </c>
     </row>
     <row r="5">
@@ -1387,13 +1394,12 @@
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>30000</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>30000</v>
-      </c>
+        <v>60000</v>
+      </c>
+      <c r="E5" s="5" t="n"/>
       <c r="F5" s="13" t="n"/>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="13" t="n"/>
+      <c r="H5" s="5" t="n">
         <v>60000</v>
       </c>
     </row>
@@ -1412,13 +1418,14 @@
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>70000</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>70000</v>
-      </c>
+        <v>570000</v>
+      </c>
+      <c r="E6" s="5" t="n"/>
       <c r="F6" s="13" t="n"/>
-      <c r="G6" s="5" t="n">
+      <c r="G6" s="13" t="n">
+        <v>-430000</v>
+      </c>
+      <c r="H6" s="5" t="n">
         <v>140000</v>
       </c>
     </row>
@@ -1445,7 +1452,8 @@
       <c r="F7" s="13" t="n">
         <v>-50000</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="13" t="n"/>
+      <c r="H7" s="5" t="n">
         <v>150000</v>
       </c>
     </row>
@@ -1470,7 +1478,8 @@
         <v>60000</v>
       </c>
       <c r="F8" s="13" t="n"/>
-      <c r="G8" s="5" t="n">
+      <c r="G8" s="13" t="n"/>
+      <c r="H8" s="5" t="n">
         <v>120000</v>
       </c>
     </row>
@@ -1481,16 +1490,19 @@
         </is>
       </c>
       <c r="D9" s="14" t="n">
-        <v>340000</v>
+        <v>1125000</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>290000</v>
+        <v>135000</v>
       </c>
       <c r="F9" s="14" t="n">
         <v>-50000</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>580000</v>
+        <v>-685000</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>525000</v>
       </c>
     </row>
     <row r="11">
@@ -1514,7 +1526,8 @@
         <v>150000</v>
       </c>
       <c r="F11" s="13" t="n"/>
-      <c r="G11" s="5" t="n">
+      <c r="G11" s="13" t="n"/>
+      <c r="H11" s="5" t="n">
         <v>300000</v>
       </c>
     </row>
@@ -1541,7 +1554,8 @@
       <c r="F12" s="13" t="n">
         <v>-40000</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="G12" s="13" t="n"/>
+      <c r="H12" s="5" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -1566,7 +1580,8 @@
         <v>85000</v>
       </c>
       <c r="F13" s="13" t="n"/>
-      <c r="G13" s="5" t="n">
+      <c r="G13" s="13" t="n"/>
+      <c r="H13" s="5" t="n">
         <v>170000</v>
       </c>
     </row>
@@ -1591,7 +1606,8 @@
         <v>45000</v>
       </c>
       <c r="F14" s="13" t="n"/>
-      <c r="G14" s="5" t="n">
+      <c r="G14" s="13" t="n"/>
+      <c r="H14" s="5" t="n">
         <v>90000</v>
       </c>
     </row>
@@ -1610,14 +1626,15 @@
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>150000</v>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>150000</v>
-      </c>
+        <v>575000</v>
+      </c>
+      <c r="E15" s="5" t="n"/>
       <c r="F15" s="13" t="n"/>
-      <c r="G15" s="5" t="n">
-        <v>300000</v>
+      <c r="G15" s="13" t="n">
+        <v>-350000</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>225000</v>
       </c>
     </row>
     <row r="16">
@@ -1641,7 +1658,8 @@
         <v>60000</v>
       </c>
       <c r="F16" s="13" t="n"/>
-      <c r="G16" s="5" t="n">
+      <c r="G16" s="13" t="n"/>
+      <c r="H16" s="5" t="n">
         <v>120000</v>
       </c>
     </row>
@@ -1652,16 +1670,19 @@
         </is>
       </c>
       <c r="D17" s="14" t="n">
-        <v>580000</v>
+        <v>1005000</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>540000</v>
+        <v>390000</v>
       </c>
       <c r="F17" s="14" t="n">
         <v>-40000</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>1080000</v>
+        <v>-350000</v>
+      </c>
+      <c r="H17" s="14" t="n">
+        <v>1005000</v>
       </c>
     </row>
     <row r="19">
@@ -1685,7 +1706,8 @@
         <v>70000</v>
       </c>
       <c r="F19" s="13" t="n"/>
-      <c r="G19" s="5" t="n">
+      <c r="G19" s="13" t="n"/>
+      <c r="H19" s="5" t="n">
         <v>140000</v>
       </c>
     </row>
@@ -1710,7 +1732,8 @@
         <v>100000</v>
       </c>
       <c r="F20" s="13" t="n"/>
-      <c r="G20" s="5" t="n">
+      <c r="G20" s="13" t="n"/>
+      <c r="H20" s="5" t="n">
         <v>200000</v>
       </c>
     </row>
@@ -1735,7 +1758,8 @@
         <v>50000</v>
       </c>
       <c r="F21" s="13" t="n"/>
-      <c r="G21" s="5" t="n">
+      <c r="G21" s="13" t="n"/>
+      <c r="H21" s="5" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -1762,7 +1786,8 @@
       <c r="F22" s="13" t="n">
         <v>-50000</v>
       </c>
-      <c r="G22" s="5" t="n">
+      <c r="G22" s="13" t="n"/>
+      <c r="H22" s="5" t="n">
         <v>120000</v>
       </c>
     </row>
@@ -1781,14 +1806,15 @@
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>170000</v>
-      </c>
-      <c r="E23" s="5" t="n">
-        <v>170000</v>
-      </c>
+        <v>875000</v>
+      </c>
+      <c r="E23" s="5" t="n"/>
       <c r="F23" s="13" t="n"/>
-      <c r="G23" s="5" t="n">
-        <v>340000</v>
+      <c r="G23" s="13" t="n">
+        <v>-620000</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>255000</v>
       </c>
     </row>
     <row r="24">
@@ -1806,13 +1832,12 @@
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>45000</v>
-      </c>
-      <c r="E24" s="5" t="n">
-        <v>45000</v>
-      </c>
+        <v>90000</v>
+      </c>
+      <c r="E24" s="5" t="n"/>
       <c r="F24" s="13" t="n"/>
-      <c r="G24" s="5" t="n">
+      <c r="G24" s="13" t="n"/>
+      <c r="H24" s="5" t="n">
         <v>90000</v>
       </c>
     </row>
@@ -1831,14 +1856,15 @@
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>120000</v>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>120000</v>
-      </c>
+        <v>870000</v>
+      </c>
+      <c r="E25" s="5" t="n"/>
       <c r="F25" s="13" t="n"/>
-      <c r="G25" s="5" t="n">
-        <v>240000</v>
+      <c r="G25" s="13" t="n">
+        <v>-690000</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>180000</v>
       </c>
     </row>
     <row r="26">
@@ -1848,36 +1874,39 @@
         </is>
       </c>
       <c r="D26" s="14" t="n">
-        <v>665000</v>
+        <v>2165000</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>615000</v>
+        <v>280000</v>
       </c>
       <c r="F26" s="14" t="n">
         <v>-50000</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>1230000</v>
+        <v>-1310000</v>
+      </c>
+      <c r="H26" s="14" t="n">
+        <v>1085000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>The pitchers' bonuses are paid half in the season-end run (October 15) and half on the following January 15. Before the January 2026 HRIS cutover the legacy payroll put the season-end halves on E45 OTHER BONUS and the January halves on E40 PERF BONUS; from January 2026 both are BPA.</t>
+          <t>The pitchers' bonuses are paid half in the season-end run (October 15) and half on the following January 15; after the last season of a contract the season-end run pays the whole season. Before the January 2026 HRIS cutover the legacy payroll put the season-end payments on E45 OTHER BONUS and the January halves on E40 PERF BONUS; from January 2026 both are BPA.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>An All-Star bonus paid in the same legacy season-end line is taken out (Ruiz 2023, Livingston 2024, Pietersz 2025). White's Cy Young bonus (November 15, 2024) is an award, not playing time.</t>
+          <t>Taken out of the season-end line: an All-Star bonus paid in it (Ruiz 2023, Livingston 2024, Pietersz 2025), and after a contract's last season the salary the contract deferred to its end (the register's salary less the salary paid, each season of the contract). White's Cy Young bonus (November 15, 2024) is an award, not playing time.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Legacy number 01661 was reissued: Yordy Benítez's lines to January 2024, Gilmar Pietersz's from 2025; legacy lines are taken by the name on the line. The October 2025 void and reissue to Reed counts once.</t>
+          <t>Legacy number 01661 was reissued: Yordy Benítez's lines in 2023, Gilmar Pietersz's from 2025; legacy lines are taken by the name on the line. The October 2025 void and reissue to Reed counts once.</t>
         </is>
       </c>
     </row>

--- a/task151/golden/pa_bonus_accrual_2027.xlsx
+++ b/task151/golden/pa_bonus_accrual_2027.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Season-end payment</t>
+          <t>Season-end payment for the season</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>January payment</t>
+          <t>January half for the season</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1892,7 +1892,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>The pitchers' bonuses are paid half in the season-end run (October 15) and half on the following January 15; after the last season of a contract the season-end run pays the whole season. Before the January 2026 HRIS cutover the legacy payroll put the season-end payments on E45 OTHER BONUS and the January halves on E40 PERF BONUS; from January 2026 both are BPA.</t>
+          <t>Payment terms per the contract register's note: one half in the October 15 run after the season and one half in the January 15 run after that, the whole in the October 15 run after a contract's last season. Before the January 2026 HRIS cutover the legacy payroll put the season-end payments on E45 OTHER BONUS and the January halves on E40 PERF BONUS; from January 2026 both are BPA. The January 2024 run paid no half to White and the January 2025 run none to Livingston: each half was paid in his next October line, which exceeds the January half after it by that half, and is shown here in the season it was payable for (White 2023, Livingston 2024).</t>
         </is>
       </c>
     </row>
